--- a/CSV/Zombie Village.xlsx
+++ b/CSV/Zombie Village.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AE8D01-734B-4510-B3B8-2FEA694EDA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB878D4-847D-9242-9436-A3CEBC474905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="1035" windowWidth="11940" windowHeight="16095" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="11500" yWindow="4080" windowWidth="10020" windowHeight="16120" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,18 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
-  <si>
-    <t>nummer</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>X</t>
   </si>
@@ -53,10 +47,7 @@
     <t>Z</t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
-    <t>/tp</t>
+    <t>Zombie Village</t>
   </si>
 </sst>
 </file>
@@ -435,97 +426,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2">
+        <v>952</v>
       </c>
       <c r="C2">
-        <v>952</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2">
         <v>4184</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3">
+        <v>3992</v>
       </c>
       <c r="C3">
-        <v>3992</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
         <v>1592</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4">
+        <v>5048</v>
       </c>
       <c r="C4">
-        <v>5048</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="B5">
+        <v>296</v>
       </c>
       <c r="C5">
-        <v>296</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
         <v>2296</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
